--- a/output/graficos_dimensiones/comunal_e_supneta_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supneta_a_2020_biobio.xlsx
@@ -108,12 +108,12 @@
     <t xml:space="preserve">Lebu</t>
   </si>
   <si>
+    <t xml:space="preserve">Quilaco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Negrete</t>
   </si>
   <si>
-    <t xml:space="preserve">Quilaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Alamos</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:08</t>
+    <t xml:space="preserve">2026-09-10 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -982,7 +982,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>8307</v>
+        <v>8308</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2020</v>
@@ -999,7 +999,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>8308</v>
+        <v>8307</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_e_supneta_a_2020_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_supneta_a_2020_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:11</t>
+    <t xml:space="preserve">2026-09-18 10:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
